--- a/docs/downloads/04/tbl_class_marovoay_maroala.xlsx
+++ b/docs/downloads/04/tbl_class_marovoay_maroala.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1.6</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,14 +457,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -532,14 +520,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>2.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -601,14 +583,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11">
-        <v>9.4</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="12">
@@ -619,19 +601,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>4.7</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -647,14 +623,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>71.40000000000001</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -670,14 +640,8 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>28.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -696,12 +660,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D15">
-        <v>10</v>
-      </c>
-      <c r="E15">
-        <v>12.3</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -742,34 +700,28 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="19">
@@ -785,14 +737,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>185</v>
-      </c>
-      <c r="E19">
-        <v>84.09999999999999</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -808,14 +754,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D20">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="E20">
-        <v>13.6</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -831,14 +777,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="22">
@@ -849,19 +795,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>72</v>
-      </c>
-      <c r="E22">
-        <v>58.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -877,14 +817,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D23">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="E23">
-        <v>36.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="24">
@@ -900,14 +840,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E24">
-        <v>4.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="25">
@@ -918,19 +858,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D25">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>51.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="26">
@@ -946,14 +886,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D26">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="E26">
-        <v>33.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="27">
@@ -969,14 +909,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D27">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="28">
@@ -992,14 +932,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E28">
-        <v>3.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="29">
@@ -1018,12 +958,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D29">
-        <v>15</v>
-      </c>
-      <c r="E29">
-        <v>55.6</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1056,19 +990,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D31">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>14.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="32">
@@ -1084,14 +1018,8 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>236</v>
-      </c>
-      <c r="E32">
-        <v>85.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1107,14 +1035,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>236</v>
+      </c>
+      <c r="E33">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6-10 ans</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D33">
-        <v>2</v>
-      </c>
-      <c r="E33">
-        <v>0.7</v>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6-10 ans</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>35</v>
+      </c>
+      <c r="E35">
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>
